--- a/data/groups.xlsx
+++ b/data/groups.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>No.</t>
   </si>
@@ -28,7 +28,13 @@
     <t>Data File Name</t>
   </si>
   <si>
-    <t/>
+    <t>https://www.facebook.com/groups/415980907903583/members</t>
+  </si>
+  <si>
+    <t>Mua Bán Quần Áo Online Giá Rẻ</t>
+  </si>
+  <si>
+    <t>1.csv</t>
   </si>
 </sst>
 </file>
@@ -36,7 +42,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,6 +70,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -203,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -217,13 +229,7 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
@@ -241,17 +247,17 @@
     <xf xfId="0" numFmtId="0" borderId="9" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -570,10 +576,10 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="15" width="13.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="16" width="64.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="71.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="16" width="35.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="13.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="64.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="71.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="14" width="35.14785714285715" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -598,105 +604,81 @@
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>4</v>
-      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>4</v>
-      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>4</v>
-      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>4</v>
-      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="20.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="21">
-      <c r="A10" s="10">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="12"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
